--- a/data_extactor/batch/151_200.xlsx
+++ b/data_extactor/batch/151_200.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sarbazi\code\sarbazi\data_extactor\batch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7689BE-4E8C-4BF0-8D98-0BF1C9DED2F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DBE041-12A3-4948-8EDE-5F45E5D6BD32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="550">
   <si>
     <t>17-1021.00</t>
   </si>
@@ -1627,6 +1627,54 @@
   </si>
   <si>
     <t>Analyze the life cycle of nanomaterials or nano-enabled products to determine environmental impact. | Assemble components, using techniques such as interference fitting, solvent bonding, adhesive bonding, heat sealing, or ultrasonic welding. | Assist nanoscientists or engineers in processing or characterizing materials according to physical or chemical properties. | Assist nanoscientists or engineers in writing process specifications or documentation. | Calibrate nanotechnology equipment, such as weighing, testing, or production equipment. | Collaborate with scientists or engineers to design or conduct experiments for the development of nanotechnology materials, components, devices, or systems. | Collect or compile nanotechnology research or engineering data. | Compare the performance or environmental impact of nanomaterials by nanoparticle size, shape, or organization. | Contribute written material or data for grant or patent applications. | Develop or modify wet chemical or industrial laboratory experimental techniques for nanoscale use. | Implement new or enhanced methods or processes for the processing, testing, or manufacture of nanotechnology materials or products. | Inspect or measure thin films of carbon nanotubes, polymers, or inorganic coatings, using a variety of techniques or analytical tools. | Maintain accurate record or batch-record documentation of nanoproduction. | Maintain work area according to cleanroom or other processing standards. | Measure emission of nanodust or nanoparticles during nanocomposite or other nano-scale production processes, using systems such as aerosol detection systems. | Measure or mix chemicals or compounds in accordance with detailed instructions or formulas. | Monitor equipment during operation to ensure adherence to specifications for characteristics such as pressure, temperature, or flow. | Monitor hazardous waste cleanup procedures to ensure proper application of nanocomposites or accomplishment of objectives. | Operate nanotechnology compounding, testing, processing, or production equipment in accordance with appropriate standard operating procedures, good manufacturing practices, hazardous material restrictions, or health and safety requirements. | Perform functional tests of nano-enhanced assemblies, components, or systems, using equipment such as torque gauges or conductivity meters. | Prepare capability data, training materials, or other documentation for transfer of processes to production. | Prepare detailed verbal or written presentations for scientists, engineers, project managers, or upper management. | Process nanoparticles or nanostructures, using technologies such as ultraviolet radiation, microwave energy, or catalysis. | Produce images or measurements, using tools or techniques such as atomic force microscopy, scanning electron microscopy, optical microscopy, particle size analysis, or zeta potential analysis. | Repair nanotechnology processing or testing equipment or submit work orders for equipment repair.</t>
+  </si>
+  <si>
+    <t>Acoustical Engineer | Applications Engineer | Design Engineer | Optical Engineer | Product Engineer | Project Engineer | Reliability Engineer | Research Engineer | Systems Engineer | Test Engineer</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | ANSYS simulation software | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | Three-dimensional 3D computer aided design CAD software | Two-dimensional 2D computer aided design CAD software | Email software | Microsoft PowerPoint | Python | Microsoft Access</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Mathematics | Active Learning | Writing | Speaking | Active Listening | Science | Monitoring | Learning Strategies</t>
+  </si>
+  <si>
+    <t>Engineering and Technology | Mathematics | Physics | Design | Computers and Electronics | English Language | Mechanical | Production and Processing | Administration and Management | Chemistry</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure | Arm-Hand Steadiness | Finger Dexterity</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Coordinate or Lead Others in Accomplishing Work Activities | Indoors, Not Environmentally Controlled | Consequence of Error | Health and Safety of Other Workers | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets</t>
+  </si>
+  <si>
+    <t>Energy Engineers, Except Wind and Solar | Mechatronics Engineers | Microsystems Engineers | Photonics Engineers | Robotics Engineers | Nanosystems Engineers | Wind Energy Engineers | Solar Energy Systems Engineers | Aerospace Engineers | Chemical Engineers | Civil Engineers | Electrical Engineers | Electronics Engineers, Except Computer | Industrial Engineers | Materials Engineers | Mechanical Engineers | Nuclear Engineers | Environmental Engineers | Computer Hardware Engineers | Architectural and Engineering Managers</t>
+  </si>
+  <si>
+    <t>Perform engineering duties in specialties not classified separately. | Research, design, and develop products, systems, components, and processes. | Prepare engineering specifications, calculations, drawings, and technical documentation. | Analyze designs using modeling, simulation, and computational methods. | Plan and conduct tests to verify that designs meet performance and safety requirements. | Evaluate test data and modify designs to correct deficiencies. | Select materials, components, and equipment based on engineering requirements and cost. | Confer with clients, vendors, and other engineers to establish design criteria. | Estimate project costs, schedules, resource needs, and technical risks. | Oversee fabrication, installation, and commissioning of engineered systems. | Investigate equipment failures and recommend corrective design or process changes. | Ensure designs comply with applicable codes, standards, and regulatory requirements. | Prepare technical reports and present findings to management and clients. | Direct the work of technicians, drafters, and junior engineering staff. | Maintain configuration control and revision records for engineering documents.</t>
+  </si>
+  <si>
+    <t>CAD Drafter | CAD Operator | CAD Technician | Design Drafter | Detailer | Drafter | Drafting Technician | Layout Drafter | Piping Drafter | Structural Drafter</t>
+  </si>
+  <si>
+    <t>Autodesk AutoCAD | Autodesk Revit | Bentley MicroStation | Dassault Systemes SolidWorks | Computer aided design and drafting software CADD | Three-dimensional 3D computer aided design CAD software | Two-dimensional 2D computer aided design CAD software | Microsoft Excel | Microsoft Word | Adobe Acrobat | Email software | Microsoft Office software</t>
+  </si>
+  <si>
+    <t>Reading Comprehension | Critical Thinking | Monitoring | Active Listening | Speaking | Mathematics | Active Learning | Writing</t>
+  </si>
+  <si>
+    <t>Design | Engineering and Technology | Mathematics | Computers and Electronics | English Language | Building and Construction | Mechanical | Production and Processing</t>
+  </si>
+  <si>
+    <t>Oral Comprehension | Written Comprehension | Oral Expression | Deductive Reasoning | Inductive Reasoning | Problem Sensitivity | Information Ordering | Near Vision | Visualization | Arm-Hand Steadiness | Finger Dexterity | Manual Dexterity | Control Precision | Multilimb Coordination | Selective Attention | Category Flexibility | Mathematical Reasoning | Far Vision | Perceptual Speed | Flexibility of Closure</t>
+  </si>
+  <si>
+    <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Written Letters and Memos | Frequency of Decision Making | Impact of Decisions on Co-workers or Company Results | Deal With External Customers or the Public in General | Importance of Repeating Same Tasks | Spend Time Making Repetitive Motions | Degree of Automation</t>
+  </si>
+  <si>
+    <t>Architectural and Civil Drafters | Electrical and Electronics Drafters | Mechanical Drafters | Civil Engineering Technologists and Technicians | Electrical and Electronic Engineering Technologists and Technicians | Mechanical Engineering Technologists and Technicians | Surveying and Mapping Technicians | Cartographers and Photogrammetrists | Architects, Except Landscape and Naval | Landscape Architects | Surveyors | Industrial Engineering Technologists and Technicians | Environmental Engineering Technologists and Technicians | Electro-Mechanical and Mechatronics Technologists and Technicians | Calibration Technologists and Technicians | Aerospace Engineering and Operations Technologists and Technicians | Civil Engineers | Mechanical Engineers | Interior Designers | Commercial and Industrial Designers</t>
+  </si>
+  <si>
+    <t>Prepare detailed drawings and plans in drafting specialties not classified separately. | Produce working drawings from sketches, specifications, and engineering calculations. | Operate computer aided design systems to create two- and three-dimensional models. | Add dimensions, tolerances, materials, and assembly notes to technical drawings. | Review drawings for accuracy, completeness, and conformance to standards. | Revise drawings to reflect design changes and maintain revision records. | Coordinate with engineers, architects, and fabricators to resolve design details. | Calculate quantities, weights, and dimensions required for drawings and estimates. | Maintain drawing files, layer standards, and template libraries. | Prepare bills of material and parts lists from design documentation. | Convert legacy drawings and scanned documents into digital formats. | Verify that drawings comply with applicable codes, symbols, and drafting conventions. | Plot, print, and distribute drawing sets to project stakeholders.</t>
   </si>
 </sst>
 </file>
@@ -2969,8 +3017,32 @@
       <c r="B30" t="s">
         <v>320</v>
       </c>
+      <c r="C30" t="s">
+        <v>534</v>
+      </c>
+      <c r="D30" t="s">
+        <v>535</v>
+      </c>
+      <c r="E30" t="s">
+        <v>536</v>
+      </c>
+      <c r="F30" t="s">
+        <v>537</v>
+      </c>
+      <c r="G30" t="s">
+        <v>538</v>
+      </c>
+      <c r="H30" t="s">
+        <v>539</v>
+      </c>
+      <c r="I30" t="s">
+        <v>540</v>
+      </c>
       <c r="J30" t="s">
         <v>321</v>
+      </c>
+      <c r="K30" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
@@ -3365,8 +3437,32 @@
       <c r="B42" t="s">
         <v>444</v>
       </c>
+      <c r="C42" t="s">
+        <v>542</v>
+      </c>
+      <c r="D42" t="s">
+        <v>543</v>
+      </c>
+      <c r="E42" t="s">
+        <v>544</v>
+      </c>
+      <c r="F42" t="s">
+        <v>545</v>
+      </c>
+      <c r="G42" t="s">
+        <v>546</v>
+      </c>
+      <c r="H42" t="s">
+        <v>547</v>
+      </c>
+      <c r="I42" t="s">
+        <v>548</v>
+      </c>
       <c r="J42" t="s">
         <v>445</v>
+      </c>
+      <c r="K42" t="s">
+        <v>549</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
